--- a/tests/fixtures/excel_tree_prefix_off/config/a/b.xlsx
+++ b/tests/fixtures/excel_tree_prefix_off/config/a/b.xlsx
@@ -4,8 +4,8 @@
   <sheets>
     <sheet name="c" sheetId="1" r:id="rId1"/>
     <sheet name="d" sheetId="2" r:id="rId2"/>
-    <sheet name="#x" sheetId="3" r:id="rId3"/>
-    <sheet name=".y" sheetId="4" r:id="rId4"/>
+    <sheet name="e.f" sheetId="3" r:id="rId3"/>
+    <sheet name="#x" sheetId="4" r:id="rId4"/>
     <sheet name="_z" sheetId="5" r:id="rId5"/>
     <sheet name="h" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
@@ -83,20 +83,20 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">p</t>
+          <t xml:space="preserve">k3</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">i64</t>
+          <t xml:space="preserve">i32</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -122,7 +122,7 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
